--- a/태화라이온스 수지계산서.xlsx
+++ b/태화라이온스 수지계산서.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1F7255-D277-4918-A289-3A5DFB04B11C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0DE09C-1950-41B6-89B0-1B67AB413D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26E54569-0732-4B05-8941-80C3AB9F876D}"/>
+    <workbookView xWindow="-25005" yWindow="-3090" windowWidth="21600" windowHeight="11295" xr2:uid="{26E54569-0732-4B05-8941-80C3AB9F876D}"/>
   </bookViews>
   <sheets>
-    <sheet name="계정별원장_439" sheetId="7" r:id="rId1"/>
-    <sheet name="수지계산서_439" sheetId="6" r:id="rId2"/>
-    <sheet name="수지계산서_438" sheetId="2" r:id="rId3"/>
-    <sheet name="계정별원장_438" sheetId="3" r:id="rId4"/>
-    <sheet name="회원별누적" sheetId="5" r:id="rId5"/>
+    <sheet name="계정별원장_439" sheetId="10" r:id="rId1"/>
+    <sheet name="수지계산서_439" sheetId="9" r:id="rId2"/>
+    <sheet name="회원별누적" sheetId="8" r:id="rId3"/>
+    <sheet name="수지계산서_438" sheetId="2" r:id="rId4"/>
+    <sheet name="계정별원장_438" sheetId="3" r:id="rId5"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId6"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="255">
   <si>
     <t>제 438차 수지 계산서</t>
   </si>
@@ -484,9 +484,6 @@
   </si>
   <si>
     <t>합  계</t>
-  </si>
-  <si>
-    <t>회원별 자진봉사금 · 발전기금 · 써클활동비  [누적]  (438차 ~ 439차)</t>
   </si>
   <si>
     <t xml:space="preserve">태화라이온스   </t>
@@ -801,9 +798,6 @@
     <t>답례품(5,000원*50개)</t>
   </si>
   <si>
-    <t>└ 부부합동 연수회 및 월례회 소계 (8건)</t>
-  </si>
-  <si>
     <t>도산급식봉사</t>
   </si>
   <si>
@@ -817,6 +811,15 @@
   </si>
   <si>
     <t>조현, 김관현, 김철홍, 김창룡, 최연식, 김춘택, 김성림, 장태원, 황순만</t>
+  </si>
+  <si>
+    <t>회원별 자진봉사금 · 발전기금 · 써클활동비  [누적]  (438차 ~ 440차)</t>
+  </si>
+  <si>
+    <t>└ 부부합동 연수회 및 월례회 소계 (3건)</t>
+  </si>
+  <si>
+    <t>└ 부부합동 연수회 및 월례회 소계 (7건)</t>
   </si>
 </sst>
 </file>
@@ -1047,6 +1050,36 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1077,9 +1110,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1089,34 +1119,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1165,6 +1168,8 @@
       <sheetName val="회원명부"/>
       <sheetName val="수지계산서_438"/>
       <sheetName val="계정별원장_438"/>
+      <sheetName val="수지계산서_440"/>
+      <sheetName val="계정별원장_440"/>
       <sheetName val="수지계산서"/>
       <sheetName val="계정별원장"/>
       <sheetName val="회원별월별"/>
@@ -1257,6 +1262,8 @@
       <sheetData sheetId="10" refreshError="1"/>
       <sheetData sheetId="11" refreshError="1"/>
       <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1578,11 +1585,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB17E067-0C21-4019-8181-78297577CA27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF1C050C-2433-43B3-A0A1-ED8EA6618EBE}">
   <sheetPr>
     <tabColor rgb="FFA6A6A6"/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -1593,26 +1600,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
-        <v>226</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="A1" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
@@ -1645,7 +1652,7 @@
         <v>38</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D5" s="5">
         <v>2080000</v>
@@ -1655,7 +1662,7 @@
         <v>2080000</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1678,11 +1685,11 @@
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="45" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
+      <c r="A7" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="13">
         <v>3110000</v>
       </c>
@@ -1691,11 +1698,11 @@
       <c r="G7" s="14"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
       <c r="D8" s="8">
         <v>3110000</v>
       </c>
@@ -1706,15 +1713,15 @@
       <c r="G8" s="16"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
-        <v>230</v>
-      </c>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
+      <c r="A10" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
@@ -1744,7 +1751,7 @@
         <v>46248</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>73</v>
@@ -1763,7 +1770,7 @@
         <v>46249</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>43</v>
@@ -1782,7 +1789,7 @@
         <v>46249</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>71</v>
@@ -1801,7 +1808,7 @@
         <v>46249</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>72</v>
@@ -1820,7 +1827,7 @@
         <v>46249</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>76</v>
@@ -1833,7 +1840,7 @@
         <v>500008</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1841,7 +1848,7 @@
         <v>46249</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>75</v>
@@ -1860,10 +1867,10 @@
         <v>46249</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D18" s="5">
         <v>100000</v>
@@ -1879,10 +1886,10 @@
         <v>46249</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D19" s="5">
         <v>100000</v>
@@ -1898,7 +1905,7 @@
         <v>46249</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>82</v>
@@ -1917,7 +1924,7 @@
         <v>46249</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>80</v>
@@ -1936,7 +1943,7 @@
         <v>46249</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>88</v>
@@ -1955,7 +1962,7 @@
         <v>46249</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>39</v>
@@ -1974,7 +1981,7 @@
         <v>46249</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>57</v>
@@ -1993,7 +2000,7 @@
         <v>46249</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -2012,7 +2019,7 @@
         <v>46249</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>41</v>
@@ -2031,7 +2038,7 @@
         <v>46249</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>79</v>
@@ -2050,10 +2057,10 @@
         <v>46249</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D28" s="5">
         <v>100000</v>
@@ -2069,10 +2076,10 @@
         <v>46249</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D29" s="5">
         <v>100000</v>
@@ -2088,10 +2095,10 @@
         <v>46249</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D30" s="5">
         <v>200000</v>
@@ -2103,11 +2110,11 @@
       <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="45" t="s">
-        <v>237</v>
-      </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
+      <c r="A31" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
       <c r="D31" s="13">
         <v>2000008</v>
       </c>
@@ -2116,11 +2123,11 @@
       <c r="G31" s="14"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="44" t="s">
+      <c r="A32" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="44"/>
-      <c r="C32" s="44"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
       <c r="D32" s="8">
         <v>2000008</v>
       </c>
@@ -2131,15 +2138,15 @@
       <c r="G32" s="16"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="40" t="s">
+      <c r="A34" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
@@ -2169,7 +2176,7 @@
         <v>46249</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>43</v>
@@ -2187,129 +2194,127 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="12">
-        <v>46257</v>
+        <v>46262</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="D37" s="5">
-        <v>300000</v>
+        <v>125000</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5">
-        <v>500000</v>
+        <v>325000</v>
       </c>
       <c r="G37" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="12">
+        <v>46262</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="5">
+        <v>125000</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5">
+        <v>450000</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="13">
+        <v>450000</v>
+      </c>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="14"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="12">
+        <v>46257</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="5">
+        <v>300000</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5">
+        <v>750000</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="44" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="44"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="8">
-        <v>500000</v>
-      </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8">
-        <v>500000</v>
-      </c>
-      <c r="G38" s="16"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="40" t="s">
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
+      <c r="D41" s="8">
+        <v>750000</v>
+      </c>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8">
+        <v>750000</v>
+      </c>
+      <c r="G41" s="16"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="11" t="s">
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B44" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C44" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D44" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E44" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G41" s="11" t="s">
+      <c r="G44" s="11" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="12">
-        <v>46249</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5">
-        <v>800000</v>
-      </c>
-      <c r="F42" s="5">
-        <v>800000</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="12">
-        <v>46249</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5">
-        <v>800000</v>
-      </c>
-      <c r="F43" s="5">
-        <v>1600000</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="12">
-        <v>46249</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5">
-        <v>1146000</v>
-      </c>
-      <c r="F44" s="5">
-        <v>2746000</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2317,18 +2322,18 @@
         <v>46249</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="5"/>
       <c r="E45" s="5">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="F45" s="5">
-        <v>3246000</v>
+        <v>800000</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2336,18 +2341,18 @@
         <v>46249</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5">
-        <v>824000</v>
+        <v>900000</v>
       </c>
       <c r="F46" s="5">
-        <v>4070000</v>
+        <v>1700000</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2355,18 +2360,18 @@
         <v>46249</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="5"/>
       <c r="E47" s="5">
-        <v>369930</v>
+        <v>1196000</v>
       </c>
       <c r="F47" s="5">
-        <v>4439930</v>
+        <v>2896000</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -2374,473 +2379,512 @@
         <v>46249</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="5"/>
       <c r="E48" s="5">
-        <v>40000</v>
+        <v>500000</v>
       </c>
       <c r="F48" s="5">
-        <v>4479930</v>
+        <v>3396000</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="12">
-        <v>46262</v>
+        <v>46249</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5">
-        <v>250000</v>
+        <v>824000</v>
       </c>
       <c r="F49" s="5">
-        <v>4729930</v>
+        <v>4220000</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13">
-        <v>4729930</v>
-      </c>
-      <c r="F50" s="13"/>
-      <c r="G50" s="14"/>
+      <c r="A50" s="12">
+        <v>46249</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5">
+        <v>469930</v>
+      </c>
+      <c r="F50" s="5">
+        <v>4689930</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="12">
-        <v>46262</v>
+        <v>46249</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="5"/>
       <c r="E51" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F51" s="5">
+        <v>4729930</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13">
+        <v>4729930</v>
+      </c>
+      <c r="F52" s="13"/>
+      <c r="G52" s="14"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="12">
+        <v>46262</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5">
         <v>39400</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F53" s="5">
         <v>4769330</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G53" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8">
+        <v>4769330</v>
+      </c>
+      <c r="F54" s="8">
+        <v>4769330</v>
+      </c>
+      <c r="G54" s="16"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="27"/>
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="12">
+        <v>46246</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5">
+        <v>8320</v>
+      </c>
+      <c r="F58" s="5">
+        <v>8320</v>
+      </c>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8">
+        <v>8320</v>
+      </c>
+      <c r="F59" s="8">
+        <v>8320</v>
+      </c>
+      <c r="G59" s="16"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="12">
+        <v>46246</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5">
+        <v>367500</v>
+      </c>
+      <c r="F63" s="5">
+        <v>367500</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8">
+        <v>367500</v>
+      </c>
+      <c r="F64" s="8">
+        <v>367500</v>
+      </c>
+      <c r="G64" s="16"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="B66" s="27"/>
+      <c r="C66" s="27"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="27"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="12">
+        <v>46240</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="44" t="s">
+      <c r="C68" s="2"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5">
+        <v>4400</v>
+      </c>
+      <c r="F68" s="5">
+        <v>4400</v>
+      </c>
+      <c r="G68" s="2"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B52" s="44"/>
-      <c r="C52" s="44"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8">
-        <v>4769330</v>
-      </c>
-      <c r="F52" s="8">
-        <v>4769330</v>
-      </c>
-      <c r="G52" s="16"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="B54" s="34"/>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="34"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="11" t="s">
+      <c r="B69" s="28"/>
+      <c r="C69" s="28"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8">
+        <v>4400</v>
+      </c>
+      <c r="F69" s="8">
+        <v>4400</v>
+      </c>
+      <c r="G69" s="16"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" s="27"/>
+      <c r="C71" s="27"/>
+      <c r="D71" s="27"/>
+      <c r="E71" s="27"/>
+      <c r="F71" s="27"/>
+      <c r="G71" s="27"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B72" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C72" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D72" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E72" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F72" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G55" s="11" t="s">
+      <c r="G72" s="11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="12">
-        <v>46246</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5">
-        <v>8320</v>
-      </c>
-      <c r="F56" s="5">
-        <v>8320</v>
-      </c>
-      <c r="G56" s="2"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="44" t="s">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="12">
+        <v>46256</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5">
+        <v>420000</v>
+      </c>
+      <c r="F73" s="5">
+        <v>420000</v>
+      </c>
+      <c r="G73" s="2"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B57" s="44"/>
-      <c r="C57" s="44"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8">
-        <v>8320</v>
-      </c>
-      <c r="F57" s="8">
-        <v>8320</v>
-      </c>
-      <c r="G57" s="16"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="B59" s="34"/>
-      <c r="C59" s="34"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="34"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B60" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G60" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="12">
-        <v>46246</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5">
-        <v>367500</v>
-      </c>
-      <c r="F61" s="5">
-        <v>367500</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="44"/>
-      <c r="C62" s="44"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8">
-        <v>367500</v>
-      </c>
-      <c r="F62" s="8">
-        <v>367500</v>
-      </c>
-      <c r="G62" s="16"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="B64" s="34"/>
-      <c r="C64" s="34"/>
-      <c r="D64" s="34"/>
-      <c r="E64" s="34"/>
-      <c r="F64" s="34"/>
-      <c r="G64" s="34"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G65" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="12">
-        <v>46240</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5">
-        <v>4400</v>
-      </c>
-      <c r="F66" s="5">
-        <v>4400</v>
-      </c>
-      <c r="G66" s="2"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="B67" s="44"/>
-      <c r="C67" s="44"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8">
-        <v>4400</v>
-      </c>
-      <c r="F67" s="8">
-        <v>4400</v>
-      </c>
-      <c r="G67" s="16"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="B69" s="34"/>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="34"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B70" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G70" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="12">
-        <v>46256</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5">
+      <c r="B74" s="28"/>
+      <c r="C74" s="28"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8">
         <v>420000</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F74" s="8">
         <v>420000</v>
       </c>
-      <c r="G71" s="2"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="44"/>
-      <c r="C72" s="44"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8">
-        <v>420000</v>
-      </c>
-      <c r="F72" s="8">
-        <v>420000</v>
-      </c>
-      <c r="G72" s="16"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="40" t="s">
+      <c r="G74" s="16"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="B75" s="34"/>
-      <c r="C75" s="34"/>
-      <c r="D75" s="34"/>
-      <c r="E75" s="34"/>
-      <c r="F75" s="34"/>
-      <c r="G75" s="34"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="17" t="s">
+      <c r="B77" s="27"/>
+      <c r="C77" s="27"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="27"/>
+      <c r="F77" s="27"/>
+      <c r="G77" s="27"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B76" s="17" t="s">
+      <c r="B78" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C76" s="17" t="s">
+      <c r="C78" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D76" s="18" t="s">
+      <c r="D78" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E76" s="41" t="s">
+      <c r="E78" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="F76" s="41"/>
-      <c r="G76" s="41"/>
-    </row>
-    <row r="77" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B77" s="5">
-        <v>250000</v>
-      </c>
-      <c r="C77" s="5">
-        <v>0</v>
-      </c>
-      <c r="D77" s="19">
-        <v>0</v>
-      </c>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="42"/>
-    </row>
-    <row r="78" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B78" s="5">
-        <v>200000</v>
-      </c>
-      <c r="C78" s="5">
-        <v>0</v>
-      </c>
-      <c r="D78" s="19">
-        <v>0</v>
-      </c>
-      <c r="E78" s="42"/>
-      <c r="F78" s="42"/>
-      <c r="G78" s="42"/>
+      <c r="F78" s="29"/>
+      <c r="G78" s="29"/>
     </row>
     <row r="79" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B79" s="5">
+        <v>250000</v>
+      </c>
+      <c r="C79" s="5">
+        <v>0</v>
+      </c>
+      <c r="D79" s="19">
+        <v>0</v>
+      </c>
+      <c r="E79" s="24"/>
+      <c r="F79" s="24"/>
+      <c r="G79" s="24"/>
+    </row>
+    <row r="80" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B80" s="5">
+        <v>200000</v>
+      </c>
+      <c r="C80" s="5">
+        <v>0</v>
+      </c>
+      <c r="D80" s="19">
+        <v>0</v>
+      </c>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+    </row>
+    <row r="81" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B79" s="5">
-        <v>100000</v>
-      </c>
-      <c r="C79" s="5">
+      <c r="B81" s="5">
+        <v>100000</v>
+      </c>
+      <c r="C81" s="5">
         <v>900000</v>
       </c>
-      <c r="D79" s="19">
+      <c r="D81" s="19">
         <v>9</v>
       </c>
-      <c r="E79" s="42" t="s">
-        <v>253</v>
-      </c>
-      <c r="F79" s="42"/>
-      <c r="G79" s="42"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="16" t="s">
+      <c r="E81" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F81" s="24"/>
+      <c r="G81" s="24"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8">
+      <c r="B82" s="8"/>
+      <c r="C82" s="8">
         <v>900000</v>
       </c>
-      <c r="D80" s="15">
+      <c r="D82" s="15">
         <v>9</v>
       </c>
-      <c r="E80" s="43"/>
-      <c r="F80" s="43"/>
-      <c r="G80" s="43"/>
+      <c r="E82" s="25"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="E78:G78"/>
     <mergeCell ref="E79:G79"/>
-    <mergeCell ref="E80:G80"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="E76:G76"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="E78:G78"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A66:G66"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A43:G43"/>
     <mergeCell ref="A52:C52"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
@@ -2855,7 +2899,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A377DDBA-B57C-40F0-85C5-B883B2ABB96C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E9C5F20-1BDD-4CD2-AF8C-F5FBD2084A2D}">
   <sheetPr>
     <tabColor rgb="FFA6A6A6"/>
   </sheetPr>
@@ -2872,363 +2916,363 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="46" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="F2" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
       <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
       <c r="I5" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="4">
         <v>7896080</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="4">
         <v>4769330</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="4">
         <v>3110000</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
       <c r="I7" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="4">
         <v>2000008</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="4">
         <v>8320</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="4">
         <v>0</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
       <c r="I9" s="4">
         <v>367500</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="4">
         <v>0</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
       <c r="I10" s="4">
         <v>4400</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
       <c r="D11" s="4">
         <v>0</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
       <c r="I11" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
       <c r="D12" s="5"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
       <c r="I12" s="4">
         <v>420000</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="5"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
       <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
       <c r="D14" s="6">
         <v>13006088</v>
       </c>
       <c r="E14" s="7"/>
-      <c r="F14" s="35" t="s">
+      <c r="F14" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
       <c r="I14" s="6">
         <v>5569550</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="4">
         <v>7436538</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="5"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="4">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="30" t="s">
+      <c r="F17" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
       <c r="I17" s="4">
-        <v>500000</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="4">
         <v>900000</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="30" t="s">
+      <c r="F18" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="4">
         <v>900000</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
       <c r="D19" s="8">
-        <v>14406088</v>
+        <v>14656088</v>
       </c>
       <c r="E19" s="9"/>
-      <c r="F19" s="32" t="s">
+      <c r="F19" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
       <c r="I19" s="8">
-        <v>6969550</v>
+        <v>7219550</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
       <c r="D20" s="5"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="25">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35">
         <v>7436538</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="25">
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="35">
         <v>45000000</v>
       </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28">
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="38">
         <v>52436538</v>
       </c>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="43">
@@ -3282,6 +3326,1560 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4062FBFD-C8CE-48F1-B883-F8B6F8DA53B6}">
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.625" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="20.625" customWidth="1"/>
+    <col min="4" max="10" width="14.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="52" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="47"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="47"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="5">
+        <v>4160000</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G6" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H6" s="5">
+        <v>300000</v>
+      </c>
+      <c r="I6" s="5">
+        <v>950000</v>
+      </c>
+      <c r="J6" s="5">
+        <v>5110000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" s="5">
+        <v>720000</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>200000</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>200000</v>
+      </c>
+      <c r="J7" s="5">
+        <v>920000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1850000</v>
+      </c>
+      <c r="E8" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F8" s="5">
+        <v>500000</v>
+      </c>
+      <c r="G8" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H8" s="5">
+        <v>200000</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1100000</v>
+      </c>
+      <c r="J8" s="5">
+        <v>3050000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1150000</v>
+      </c>
+      <c r="E9" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F9" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G9" s="5">
+        <v>200000</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>450000</v>
+      </c>
+      <c r="J9" s="5">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>5</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="5">
+        <v>800000</v>
+      </c>
+      <c r="E10" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F10" s="5">
+        <v>500000</v>
+      </c>
+      <c r="G10" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H10" s="5">
+        <v>100000</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1000000</v>
+      </c>
+      <c r="J10" s="5">
+        <v>1900000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="5">
+        <v>455000</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G11" s="5">
+        <v>200000</v>
+      </c>
+      <c r="H11" s="5">
+        <v>200000</v>
+      </c>
+      <c r="I11" s="5">
+        <v>650000</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1105000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="5">
+        <v>125000</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>250000</v>
+      </c>
+      <c r="J12" s="5">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" s="5">
+        <v>100000</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="21">
+        <v>9</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D14" s="22">
+        <v>0</v>
+      </c>
+      <c r="E14" s="22">
+        <v>0</v>
+      </c>
+      <c r="F14" s="22">
+        <v>0</v>
+      </c>
+      <c r="G14" s="22">
+        <v>0</v>
+      </c>
+      <c r="H14" s="22">
+        <v>0</v>
+      </c>
+      <c r="I14" s="22">
+        <v>0</v>
+      </c>
+      <c r="J14" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A15" s="21">
+        <v>10</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="22">
+        <v>0</v>
+      </c>
+      <c r="E15" s="22">
+        <v>0</v>
+      </c>
+      <c r="F15" s="22">
+        <v>0</v>
+      </c>
+      <c r="G15" s="22">
+        <v>0</v>
+      </c>
+      <c r="H15" s="22">
+        <v>0</v>
+      </c>
+      <c r="I15" s="22">
+        <v>0</v>
+      </c>
+      <c r="J15" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" s="5">
+        <v>200000</v>
+      </c>
+      <c r="E16" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F16" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G16" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>650000</v>
+      </c>
+      <c r="J16" s="5">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="5">
+        <v>100000</v>
+      </c>
+      <c r="E17" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>400000</v>
+      </c>
+      <c r="J17" s="5">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="21">
+        <v>13</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" s="22">
+        <v>0</v>
+      </c>
+      <c r="E18" s="22">
+        <v>0</v>
+      </c>
+      <c r="F18" s="22">
+        <v>0</v>
+      </c>
+      <c r="G18" s="22">
+        <v>0</v>
+      </c>
+      <c r="H18" s="22">
+        <v>0</v>
+      </c>
+      <c r="I18" s="22">
+        <v>0</v>
+      </c>
+      <c r="J18" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="21">
+        <v>14</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="22">
+        <v>0</v>
+      </c>
+      <c r="E19" s="22">
+        <v>0</v>
+      </c>
+      <c r="F19" s="22">
+        <v>0</v>
+      </c>
+      <c r="G19" s="22">
+        <v>0</v>
+      </c>
+      <c r="H19" s="22">
+        <v>0</v>
+      </c>
+      <c r="I19" s="22">
+        <v>0</v>
+      </c>
+      <c r="J19" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="21">
+        <v>15</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" s="22">
+        <v>0</v>
+      </c>
+      <c r="E20" s="22">
+        <v>0</v>
+      </c>
+      <c r="F20" s="22">
+        <v>0</v>
+      </c>
+      <c r="G20" s="22">
+        <v>0</v>
+      </c>
+      <c r="H20" s="22">
+        <v>0</v>
+      </c>
+      <c r="I20" s="22">
+        <v>0</v>
+      </c>
+      <c r="J20" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D21" s="5">
+        <v>100000</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>400000</v>
+      </c>
+      <c r="J21" s="5">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>17</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="5">
+        <v>300000</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G22" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>650000</v>
+      </c>
+      <c r="J22" s="5">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>18</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D23" s="5">
+        <v>200000</v>
+      </c>
+      <c r="E23" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F23" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G23" s="5">
+        <v>200000</v>
+      </c>
+      <c r="H23" s="5">
+        <v>100000</v>
+      </c>
+      <c r="I23" s="5">
+        <v>550000</v>
+      </c>
+      <c r="J23" s="5">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D24" s="5">
+        <v>300000</v>
+      </c>
+      <c r="E24" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H24" s="5">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5">
+        <v>400000</v>
+      </c>
+      <c r="J24" s="5">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>20</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D25" s="5">
+        <v>100000</v>
+      </c>
+      <c r="E25" s="5">
+        <v>100008</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H25" s="5">
+        <v>200000</v>
+      </c>
+      <c r="I25" s="5">
+        <v>600000</v>
+      </c>
+      <c r="J25" s="5">
+        <v>800008</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>21</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D26" s="5">
+        <v>550000</v>
+      </c>
+      <c r="E26" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F26" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G26" s="5">
+        <v>200000</v>
+      </c>
+      <c r="H26" s="5">
+        <v>100000</v>
+      </c>
+      <c r="I26" s="5">
+        <v>550000</v>
+      </c>
+      <c r="J26" s="5">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>22</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1190000</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5">
+        <v>500000</v>
+      </c>
+      <c r="G27" s="5">
+        <v>200000</v>
+      </c>
+      <c r="H27" s="5">
+        <v>100000</v>
+      </c>
+      <c r="I27" s="5">
+        <v>800000</v>
+      </c>
+      <c r="J27" s="5">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>23</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="5">
+        <v>100000</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5">
+        <v>200000</v>
+      </c>
+      <c r="H28" s="5">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5">
+        <v>200000</v>
+      </c>
+      <c r="J28" s="5">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>24</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D29" s="5">
+        <v>100000</v>
+      </c>
+      <c r="E29" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F29" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G29" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H29" s="5">
+        <v>100000</v>
+      </c>
+      <c r="I29" s="5">
+        <v>750000</v>
+      </c>
+      <c r="J29" s="5">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>25</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" s="5">
+        <v>300000</v>
+      </c>
+      <c r="E30" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F30" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G30" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H30" s="5">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5">
+        <v>650000</v>
+      </c>
+      <c r="J30" s="5">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>26</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="5">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G31" s="5">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5">
+        <v>250000</v>
+      </c>
+      <c r="J31" s="5">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="21">
+        <v>27</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D32" s="22">
+        <v>0</v>
+      </c>
+      <c r="E32" s="22">
+        <v>0</v>
+      </c>
+      <c r="F32" s="22">
+        <v>0</v>
+      </c>
+      <c r="G32" s="22">
+        <v>0</v>
+      </c>
+      <c r="H32" s="22">
+        <v>0</v>
+      </c>
+      <c r="I32" s="22">
+        <v>0</v>
+      </c>
+      <c r="J32" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>28</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" s="5">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F33" s="5">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5">
+        <v>200000</v>
+      </c>
+      <c r="I33" s="5">
+        <v>200000</v>
+      </c>
+      <c r="J33" s="5">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>29</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D34" s="5">
+        <v>0</v>
+      </c>
+      <c r="E34" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F34" s="5">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>30</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D35" s="5">
+        <v>200000</v>
+      </c>
+      <c r="E35" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F35" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G35" s="5">
+        <v>200000</v>
+      </c>
+      <c r="H35" s="5">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5">
+        <v>450000</v>
+      </c>
+      <c r="J35" s="5">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>31</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D36" s="5">
+        <v>80000</v>
+      </c>
+      <c r="E36" s="5">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5">
+        <v>0</v>
+      </c>
+      <c r="G36" s="5">
+        <v>400000</v>
+      </c>
+      <c r="H36" s="5">
+        <v>100000</v>
+      </c>
+      <c r="I36" s="5">
+        <v>500000</v>
+      </c>
+      <c r="J36" s="5">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>32</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D37" s="5">
+        <v>500000</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G37" s="5">
+        <v>200000</v>
+      </c>
+      <c r="H37" s="5">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5">
+        <v>450000</v>
+      </c>
+      <c r="J37" s="5">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="21">
+        <v>33</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D38" s="22">
+        <v>0</v>
+      </c>
+      <c r="E38" s="22">
+        <v>0</v>
+      </c>
+      <c r="F38" s="22">
+        <v>0</v>
+      </c>
+      <c r="G38" s="22">
+        <v>0</v>
+      </c>
+      <c r="H38" s="22">
+        <v>0</v>
+      </c>
+      <c r="I38" s="22">
+        <v>0</v>
+      </c>
+      <c r="J38" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>34</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D39" s="5">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5">
+        <v>100000</v>
+      </c>
+      <c r="I39" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J39" s="5">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>35</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D40" s="5">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5">
+        <v>0</v>
+      </c>
+      <c r="F40" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G40" s="5">
+        <v>0</v>
+      </c>
+      <c r="H40" s="5">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5">
+        <v>250000</v>
+      </c>
+      <c r="J40" s="5">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>36</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D41" s="5">
+        <v>300000</v>
+      </c>
+      <c r="E41" s="5">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5">
+        <v>100000</v>
+      </c>
+      <c r="I41" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J41" s="5">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>37</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D42" s="5">
+        <v>400000</v>
+      </c>
+      <c r="E42" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F42" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G42" s="5">
+        <v>200000</v>
+      </c>
+      <c r="H42" s="5">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5">
+        <v>450000</v>
+      </c>
+      <c r="J42" s="5">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="33" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>38</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="D43" s="5">
+        <v>400000</v>
+      </c>
+      <c r="E43" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F43" s="5">
+        <v>250000</v>
+      </c>
+      <c r="G43" s="5">
+        <v>200000</v>
+      </c>
+      <c r="H43" s="5">
+        <v>200000</v>
+      </c>
+      <c r="I43" s="5">
+        <v>650000</v>
+      </c>
+      <c r="J43" s="5">
+        <v>1150000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="21">
+        <v>39</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D44" s="22">
+        <v>0</v>
+      </c>
+      <c r="E44" s="22">
+        <v>0</v>
+      </c>
+      <c r="F44" s="22">
+        <v>0</v>
+      </c>
+      <c r="G44" s="22">
+        <v>0</v>
+      </c>
+      <c r="H44" s="22">
+        <v>0</v>
+      </c>
+      <c r="I44" s="22">
+        <v>0</v>
+      </c>
+      <c r="J44" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="21">
+        <v>40</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D45" s="22">
+        <v>0</v>
+      </c>
+      <c r="E45" s="22">
+        <v>0</v>
+      </c>
+      <c r="F45" s="22">
+        <v>0</v>
+      </c>
+      <c r="G45" s="22">
+        <v>0</v>
+      </c>
+      <c r="H45" s="22">
+        <v>0</v>
+      </c>
+      <c r="I45" s="22">
+        <v>0</v>
+      </c>
+      <c r="J45" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>41</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D46" s="5">
+        <v>0</v>
+      </c>
+      <c r="E46" s="5">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5">
+        <v>0</v>
+      </c>
+      <c r="G46" s="5">
+        <v>0</v>
+      </c>
+      <c r="H46" s="5">
+        <v>100000</v>
+      </c>
+      <c r="I46" s="5">
+        <v>100000</v>
+      </c>
+      <c r="J46" s="5">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="49"/>
+      <c r="H47" s="49"/>
+      <c r="I47" s="49"/>
+      <c r="J47" s="49"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>42</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D48" s="5">
+        <v>0</v>
+      </c>
+      <c r="E48" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F48" s="5">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5">
+        <v>0</v>
+      </c>
+      <c r="H48" s="5">
+        <v>0</v>
+      </c>
+      <c r="I48" s="5">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>43</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D49" s="5">
+        <v>0</v>
+      </c>
+      <c r="E49" s="5">
+        <v>100000</v>
+      </c>
+      <c r="F49" s="5">
+        <v>0</v>
+      </c>
+      <c r="G49" s="5">
+        <v>0</v>
+      </c>
+      <c r="H49" s="5">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5">
+        <v>0</v>
+      </c>
+      <c r="J49" s="5">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>44</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D50" s="5">
+        <v>0</v>
+      </c>
+      <c r="E50" s="5">
+        <v>200000</v>
+      </c>
+      <c r="F50" s="5">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5">
+        <v>0</v>
+      </c>
+      <c r="H50" s="5">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="B51" s="50"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="8">
+        <v>14780000</v>
+      </c>
+      <c r="E51" s="8">
+        <v>2000008</v>
+      </c>
+      <c r="F51" s="8">
+        <v>5500000</v>
+      </c>
+      <c r="G51" s="8">
+        <v>7000000</v>
+      </c>
+      <c r="H51" s="8">
+        <v>2200000</v>
+      </c>
+      <c r="I51" s="8">
+        <v>14700000</v>
+      </c>
+      <c r="J51" s="8">
+        <v>31480008</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="J4:J5"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5833D11-9C2A-4647-9AE3-338402FF7A42}">
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FFA6A6A6"/>
@@ -3299,366 +4897,402 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="A1" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="F2" s="38" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
       <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
       <c r="I5" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="4">
         <v>10928466</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="4">
         <v>2987300</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="4">
         <v>5150000</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
       <c r="I7" s="4">
         <v>1100000</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="4">
         <v>0</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="4">
         <v>54120</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="4">
         <v>0</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
       <c r="I9" s="4">
         <v>4704219</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="4">
         <v>0</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
       <c r="I10" s="4">
         <v>115000</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
       <c r="D11" s="4">
         <v>1108253</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
       <c r="I11" s="4">
         <v>230000</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
       <c r="D12" s="5"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
       <c r="I12" s="4">
         <v>100000</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="5"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
       <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
       <c r="D14" s="6">
         <v>17186719</v>
       </c>
       <c r="E14" s="7"/>
-      <c r="F14" s="35" t="s">
+      <c r="F14" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="45"/>
       <c r="I14" s="6">
         <v>9290639</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="4">
         <v>7896080</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="5"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="4">
         <v>14030000</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="30" t="s">
+      <c r="F17" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
       <c r="I17" s="4">
         <v>14030000</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="4">
         <v>13800000</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="30" t="s">
+      <c r="F18" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="4">
         <v>13800000</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
       <c r="D19" s="8">
         <v>45016719</v>
       </c>
       <c r="E19" s="9"/>
-      <c r="F19" s="32" t="s">
+      <c r="F19" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
       <c r="I19" s="8">
         <v>37120639</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
       <c r="D20" s="5"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="25">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35">
         <v>7896080</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="25">
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="35">
         <v>45000000</v>
       </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="28">
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="38">
         <v>52896080</v>
       </c>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:I23"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="F8:H8"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="A1:I1"/>
@@ -3666,49 +5300,13 @@
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="F4:I4"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:I21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:I23"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56350700-1208-4D36-AB92-289CCC1B49ED}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFA6A6A6"/>
@@ -3724,26 +5322,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
@@ -3864,11 +5462,11 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="13">
         <v>5150000</v>
       </c>
@@ -3877,11 +5475,11 @@
       <c r="G10" s="14"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="8">
         <v>5150000</v>
       </c>
@@ -3892,15 +5490,15 @@
       <c r="G11" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
@@ -3962,11 +5560,11 @@
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="44" t="s">
+      <c r="A17" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
       <c r="D17" s="8">
         <v>1108253</v>
       </c>
@@ -3977,15 +5575,15 @@
       <c r="G17" s="16"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
@@ -4053,11 +5651,11 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="46"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
       <c r="D23" s="13">
         <v>850000</v>
       </c>
@@ -4171,11 +5769,11 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="45" t="s">
+      <c r="A29" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="46"/>
-      <c r="C29" s="46"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
       <c r="D29" s="13">
         <v>900000</v>
       </c>
@@ -4247,11 +5845,11 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="45" t="s">
+      <c r="A33" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
       <c r="D33" s="13">
         <v>920000</v>
       </c>
@@ -4716,11 +6314,11 @@
       <c r="G57" s="2"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="45" t="s">
+      <c r="A58" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B58" s="46"/>
-      <c r="C58" s="46"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
       <c r="D58" s="13">
         <v>3400000</v>
       </c>
@@ -4881,11 +6479,11 @@
       <c r="G66" s="2"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="45" t="s">
+      <c r="A67" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="B67" s="46"/>
-      <c r="C67" s="46"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
       <c r="D67" s="13">
         <v>3000000</v>
       </c>
@@ -5103,11 +6701,11 @@
       <c r="G78" s="2"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="45" t="s">
+      <c r="A79" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="B79" s="46"/>
-      <c r="C79" s="46"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="31"/>
       <c r="D79" s="13">
         <v>2890000</v>
       </c>
@@ -5211,11 +6809,11 @@
       <c r="G84" s="2"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="45" t="s">
+      <c r="A85" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="B85" s="46"/>
-      <c r="C85" s="46"/>
+      <c r="B85" s="31"/>
+      <c r="C85" s="31"/>
       <c r="D85" s="13">
         <v>200000</v>
       </c>
@@ -5319,11 +6917,11 @@
       <c r="G90" s="2"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="44" t="s">
+      <c r="A91" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B91" s="44"/>
-      <c r="C91" s="44"/>
+      <c r="B91" s="28"/>
+      <c r="C91" s="28"/>
       <c r="D91" s="8">
         <v>14030000</v>
       </c>
@@ -5334,15 +6932,15 @@
       <c r="G91" s="16"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="40" t="s">
+      <c r="A93" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B93" s="34"/>
-      <c r="C93" s="34"/>
-      <c r="D93" s="34"/>
-      <c r="E93" s="34"/>
-      <c r="F93" s="34"/>
-      <c r="G93" s="34"/>
+      <c r="B93" s="27"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
+      <c r="F93" s="27"/>
+      <c r="G93" s="27"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="11" t="s">
@@ -5444,11 +7042,11 @@
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="45" t="s">
+      <c r="A99" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="B99" s="46"/>
-      <c r="C99" s="46"/>
+      <c r="B99" s="31"/>
+      <c r="C99" s="31"/>
       <c r="D99" s="13"/>
       <c r="E99" s="13">
         <v>1953500</v>
@@ -5559,11 +7157,11 @@
       <c r="G105" s="2"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" s="44" t="s">
+      <c r="A106" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B106" s="44"/>
-      <c r="C106" s="44"/>
+      <c r="B106" s="28"/>
+      <c r="C106" s="28"/>
       <c r="D106" s="8"/>
       <c r="E106" s="8">
         <v>2987300</v>
@@ -5574,15 +7172,15 @@
       <c r="G106" s="16"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" s="40" t="s">
+      <c r="A108" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="B108" s="34"/>
-      <c r="C108" s="34"/>
-      <c r="D108" s="34"/>
-      <c r="E108" s="34"/>
-      <c r="F108" s="34"/>
-      <c r="G108" s="34"/>
+      <c r="B108" s="27"/>
+      <c r="C108" s="27"/>
+      <c r="D108" s="27"/>
+      <c r="E108" s="27"/>
+      <c r="F108" s="27"/>
+      <c r="G108" s="27"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="11" t="s">
@@ -5659,11 +7257,11 @@
       <c r="G112" s="2"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" s="44" t="s">
+      <c r="A113" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B113" s="44"/>
-      <c r="C113" s="44"/>
+      <c r="B113" s="28"/>
+      <c r="C113" s="28"/>
       <c r="D113" s="8"/>
       <c r="E113" s="8">
         <v>1100000</v>
@@ -5674,15 +7272,15 @@
       <c r="G113" s="16"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" s="40" t="s">
+      <c r="A115" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="B115" s="34"/>
-      <c r="C115" s="34"/>
-      <c r="D115" s="34"/>
-      <c r="E115" s="34"/>
-      <c r="F115" s="34"/>
-      <c r="G115" s="34"/>
+      <c r="B115" s="27"/>
+      <c r="C115" s="27"/>
+      <c r="D115" s="27"/>
+      <c r="E115" s="27"/>
+      <c r="F115" s="27"/>
+      <c r="G115" s="27"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="11" t="s">
@@ -5744,11 +7342,11 @@
       <c r="G118" s="2"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="44" t="s">
+      <c r="A119" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B119" s="44"/>
-      <c r="C119" s="44"/>
+      <c r="B119" s="28"/>
+      <c r="C119" s="28"/>
       <c r="D119" s="8"/>
       <c r="E119" s="8">
         <v>54120</v>
@@ -5759,15 +7357,15 @@
       <c r="G119" s="16"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="40" t="s">
+      <c r="A121" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="B121" s="34"/>
-      <c r="C121" s="34"/>
-      <c r="D121" s="34"/>
-      <c r="E121" s="34"/>
-      <c r="F121" s="34"/>
-      <c r="G121" s="34"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="27"/>
+      <c r="D121" s="27"/>
+      <c r="E121" s="27"/>
+      <c r="F121" s="27"/>
+      <c r="G121" s="27"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
@@ -5865,11 +7463,11 @@
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="44" t="s">
+      <c r="A127" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B127" s="44"/>
-      <c r="C127" s="44"/>
+      <c r="B127" s="28"/>
+      <c r="C127" s="28"/>
       <c r="D127" s="8"/>
       <c r="E127" s="8">
         <v>4704219</v>
@@ -5880,15 +7478,15 @@
       <c r="G127" s="16"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="40" t="s">
+      <c r="A129" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="B129" s="34"/>
-      <c r="C129" s="34"/>
-      <c r="D129" s="34"/>
-      <c r="E129" s="34"/>
-      <c r="F129" s="34"/>
-      <c r="G129" s="34"/>
+      <c r="B129" s="27"/>
+      <c r="C129" s="27"/>
+      <c r="D129" s="27"/>
+      <c r="E129" s="27"/>
+      <c r="F129" s="27"/>
+      <c r="G129" s="27"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="11" t="s">
@@ -5948,11 +7546,11 @@
       <c r="G132" s="2"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="44" t="s">
+      <c r="A133" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B133" s="44"/>
-      <c r="C133" s="44"/>
+      <c r="B133" s="28"/>
+      <c r="C133" s="28"/>
       <c r="D133" s="8"/>
       <c r="E133" s="8">
         <v>115000</v>
@@ -5963,15 +7561,15 @@
       <c r="G133" s="16"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" s="40" t="s">
+      <c r="A135" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="B135" s="34"/>
-      <c r="C135" s="34"/>
-      <c r="D135" s="34"/>
-      <c r="E135" s="34"/>
-      <c r="F135" s="34"/>
-      <c r="G135" s="34"/>
+      <c r="B135" s="27"/>
+      <c r="C135" s="27"/>
+      <c r="D135" s="27"/>
+      <c r="E135" s="27"/>
+      <c r="F135" s="27"/>
+      <c r="G135" s="27"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="11" t="s">
@@ -6031,11 +7629,11 @@
       <c r="G138" s="2"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" s="44" t="s">
+      <c r="A139" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B139" s="44"/>
-      <c r="C139" s="44"/>
+      <c r="B139" s="28"/>
+      <c r="C139" s="28"/>
       <c r="D139" s="8"/>
       <c r="E139" s="8">
         <v>230000</v>
@@ -6046,15 +7644,15 @@
       <c r="G139" s="16"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141" s="40" t="s">
+      <c r="A141" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="B141" s="34"/>
-      <c r="C141" s="34"/>
-      <c r="D141" s="34"/>
-      <c r="E141" s="34"/>
-      <c r="F141" s="34"/>
-      <c r="G141" s="34"/>
+      <c r="B141" s="27"/>
+      <c r="C141" s="27"/>
+      <c r="D141" s="27"/>
+      <c r="E141" s="27"/>
+      <c r="F141" s="27"/>
+      <c r="G141" s="27"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
@@ -6099,11 +7697,11 @@
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" s="44" t="s">
+      <c r="A144" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="B144" s="44"/>
-      <c r="C144" s="44"/>
+      <c r="B144" s="28"/>
+      <c r="C144" s="28"/>
       <c r="D144" s="8"/>
       <c r="E144" s="8">
         <v>100000</v>
@@ -6114,15 +7712,15 @@
       <c r="G144" s="16"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" s="40" t="s">
+      <c r="A147" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="B147" s="34"/>
-      <c r="C147" s="34"/>
-      <c r="D147" s="34"/>
-      <c r="E147" s="34"/>
-      <c r="F147" s="34"/>
-      <c r="G147" s="34"/>
+      <c r="B147" s="27"/>
+      <c r="C147" s="27"/>
+      <c r="D147" s="27"/>
+      <c r="E147" s="27"/>
+      <c r="F147" s="27"/>
+      <c r="G147" s="27"/>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="17" t="s">
@@ -6137,11 +7735,11 @@
       <c r="D148" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E148" s="41" t="s">
+      <c r="E148" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="F148" s="41"/>
-      <c r="G148" s="41"/>
+      <c r="F148" s="29"/>
+      <c r="G148" s="29"/>
     </row>
     <row r="149" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
@@ -6156,11 +7754,11 @@
       <c r="D149" s="19">
         <v>22</v>
       </c>
-      <c r="E149" s="42" t="s">
+      <c r="E149" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="F149" s="42"/>
-      <c r="G149" s="42"/>
+      <c r="F149" s="24"/>
+      <c r="G149" s="24"/>
     </row>
     <row r="150" spans="1:7" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
@@ -6175,11 +7773,11 @@
       <c r="D150" s="19">
         <v>35</v>
       </c>
-      <c r="E150" s="42" t="s">
+      <c r="E150" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="F150" s="42"/>
-      <c r="G150" s="42"/>
+      <c r="F150" s="24"/>
+      <c r="G150" s="24"/>
     </row>
     <row r="151" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
@@ -6194,11 +7792,11 @@
       <c r="D151" s="19">
         <v>13</v>
       </c>
-      <c r="E151" s="42" t="s">
+      <c r="E151" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="F151" s="42"/>
-      <c r="G151" s="42"/>
+      <c r="F151" s="24"/>
+      <c r="G151" s="24"/>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="16" t="s">
@@ -6211,12 +7809,36 @@
       <c r="D152" s="15">
         <v>70</v>
       </c>
-      <c r="E152" s="43"/>
-      <c r="F152" s="43"/>
-      <c r="G152" s="43"/>
+      <c r="E152" s="25"/>
+      <c r="F152" s="25"/>
+      <c r="G152" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="E152:G152"/>
+    <mergeCell ref="A129:G129"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A135:G135"/>
+    <mergeCell ref="A139:C139"/>
+    <mergeCell ref="A141:G141"/>
+    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="A147:G147"/>
+    <mergeCell ref="E148:G148"/>
+    <mergeCell ref="E149:G149"/>
+    <mergeCell ref="E150:G150"/>
+    <mergeCell ref="E151:G151"/>
+    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A93:G93"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A115:G115"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A121:G121"/>
     <mergeCell ref="A67:C67"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
@@ -6229,1584 +7851,6 @@
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A127:C127"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A93:G93"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A108:G108"/>
-    <mergeCell ref="A113:C113"/>
-    <mergeCell ref="A115:G115"/>
-    <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A121:G121"/>
-    <mergeCell ref="E152:G152"/>
-    <mergeCell ref="A129:G129"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A135:G135"/>
-    <mergeCell ref="A139:C139"/>
-    <mergeCell ref="A141:G141"/>
-    <mergeCell ref="A144:C144"/>
-    <mergeCell ref="A147:G147"/>
-    <mergeCell ref="E148:G148"/>
-    <mergeCell ref="E149:G149"/>
-    <mergeCell ref="E150:G150"/>
-    <mergeCell ref="E151:G151"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40493282-61A0-4B63-A93B-8C39B707011F}">
-  <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="6.625" customWidth="1"/>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="10" width="14.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="52" t="s">
-        <v>147</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="F4" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="39"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D6" s="5">
-        <v>4160000</v>
-      </c>
-      <c r="E6" s="5">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G6" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H6" s="5">
-        <v>300000</v>
-      </c>
-      <c r="I6" s="5">
-        <v>950000</v>
-      </c>
-      <c r="J6" s="5">
-        <v>5110000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>2</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="5">
-        <v>720000</v>
-      </c>
-      <c r="E7" s="5">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
-        <v>200000</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
-        <v>200000</v>
-      </c>
-      <c r="J7" s="5">
-        <v>920000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>3</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1850000</v>
-      </c>
-      <c r="E8" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F8" s="5">
-        <v>500000</v>
-      </c>
-      <c r="G8" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H8" s="5">
-        <v>200000</v>
-      </c>
-      <c r="I8" s="5">
-        <v>1100000</v>
-      </c>
-      <c r="J8" s="5">
-        <v>3050000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1150000</v>
-      </c>
-      <c r="E9" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F9" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G9" s="5">
-        <v>200000</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <v>450000</v>
-      </c>
-      <c r="J9" s="5">
-        <v>1700000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>5</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D10" s="5">
-        <v>800000</v>
-      </c>
-      <c r="E10" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F10" s="5">
-        <v>500000</v>
-      </c>
-      <c r="G10" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H10" s="5">
-        <v>100000</v>
-      </c>
-      <c r="I10" s="5">
-        <v>1000000</v>
-      </c>
-      <c r="J10" s="5">
-        <v>1900000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D11" s="5">
-        <v>330000</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G11" s="5">
-        <v>200000</v>
-      </c>
-      <c r="H11" s="5">
-        <v>200000</v>
-      </c>
-      <c r="I11" s="5">
-        <v>650000</v>
-      </c>
-      <c r="J11" s="5">
-        <v>980000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>7</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5">
-        <v>250000</v>
-      </c>
-      <c r="J12" s="5">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>8</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D13" s="5">
-        <v>100000</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
-        <v>9</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="D14" s="22">
-        <v>0</v>
-      </c>
-      <c r="E14" s="22">
-        <v>0</v>
-      </c>
-      <c r="F14" s="22">
-        <v>0</v>
-      </c>
-      <c r="G14" s="22">
-        <v>0</v>
-      </c>
-      <c r="H14" s="22">
-        <v>0</v>
-      </c>
-      <c r="I14" s="22">
-        <v>0</v>
-      </c>
-      <c r="J14" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A15" s="21">
-        <v>10</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" s="22">
-        <v>0</v>
-      </c>
-      <c r="E15" s="22">
-        <v>0</v>
-      </c>
-      <c r="F15" s="22">
-        <v>0</v>
-      </c>
-      <c r="G15" s="22">
-        <v>0</v>
-      </c>
-      <c r="H15" s="22">
-        <v>0</v>
-      </c>
-      <c r="I15" s="22">
-        <v>0</v>
-      </c>
-      <c r="J15" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>11</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D16" s="5">
-        <v>200000</v>
-      </c>
-      <c r="E16" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F16" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G16" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H16" s="5">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5">
-        <v>650000</v>
-      </c>
-      <c r="J16" s="5">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>12</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="D17" s="5">
-        <v>100000</v>
-      </c>
-      <c r="E17" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F17" s="5">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H17" s="5">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5">
-        <v>400000</v>
-      </c>
-      <c r="J17" s="5">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="21">
-        <v>13</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="D18" s="22">
-        <v>0</v>
-      </c>
-      <c r="E18" s="22">
-        <v>0</v>
-      </c>
-      <c r="F18" s="22">
-        <v>0</v>
-      </c>
-      <c r="G18" s="22">
-        <v>0</v>
-      </c>
-      <c r="H18" s="22">
-        <v>0</v>
-      </c>
-      <c r="I18" s="22">
-        <v>0</v>
-      </c>
-      <c r="J18" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="21">
-        <v>14</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D19" s="22">
-        <v>0</v>
-      </c>
-      <c r="E19" s="22">
-        <v>0</v>
-      </c>
-      <c r="F19" s="22">
-        <v>0</v>
-      </c>
-      <c r="G19" s="22">
-        <v>0</v>
-      </c>
-      <c r="H19" s="22">
-        <v>0</v>
-      </c>
-      <c r="I19" s="22">
-        <v>0</v>
-      </c>
-      <c r="J19" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="21">
-        <v>15</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="D20" s="22">
-        <v>0</v>
-      </c>
-      <c r="E20" s="22">
-        <v>0</v>
-      </c>
-      <c r="F20" s="22">
-        <v>0</v>
-      </c>
-      <c r="G20" s="22">
-        <v>0</v>
-      </c>
-      <c r="H20" s="22">
-        <v>0</v>
-      </c>
-      <c r="I20" s="22">
-        <v>0</v>
-      </c>
-      <c r="J20" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>16</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D21" s="5">
-        <v>100000</v>
-      </c>
-      <c r="E21" s="5">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H21" s="5">
-        <v>0</v>
-      </c>
-      <c r="I21" s="5">
-        <v>400000</v>
-      </c>
-      <c r="J21" s="5">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>17</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="D22" s="5">
-        <v>300000</v>
-      </c>
-      <c r="E22" s="5">
-        <v>0</v>
-      </c>
-      <c r="F22" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G22" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H22" s="5">
-        <v>0</v>
-      </c>
-      <c r="I22" s="5">
-        <v>650000</v>
-      </c>
-      <c r="J22" s="5">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>18</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D23" s="5">
-        <v>200000</v>
-      </c>
-      <c r="E23" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F23" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G23" s="5">
-        <v>200000</v>
-      </c>
-      <c r="H23" s="5">
-        <v>100000</v>
-      </c>
-      <c r="I23" s="5">
-        <v>550000</v>
-      </c>
-      <c r="J23" s="5">
-        <v>850000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>19</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D24" s="5">
-        <v>300000</v>
-      </c>
-      <c r="E24" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F24" s="5">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H24" s="5">
-        <v>0</v>
-      </c>
-      <c r="I24" s="5">
-        <v>400000</v>
-      </c>
-      <c r="J24" s="5">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>20</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="D25" s="5">
-        <v>100000</v>
-      </c>
-      <c r="E25" s="5">
-        <v>100008</v>
-      </c>
-      <c r="F25" s="5">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H25" s="5">
-        <v>200000</v>
-      </c>
-      <c r="I25" s="5">
-        <v>600000</v>
-      </c>
-      <c r="J25" s="5">
-        <v>800008</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>21</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D26" s="5">
-        <v>550000</v>
-      </c>
-      <c r="E26" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F26" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G26" s="5">
-        <v>200000</v>
-      </c>
-      <c r="H26" s="5">
-        <v>100000</v>
-      </c>
-      <c r="I26" s="5">
-        <v>550000</v>
-      </c>
-      <c r="J26" s="5">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>22</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="D27" s="5">
-        <v>1190000</v>
-      </c>
-      <c r="E27" s="5">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5">
-        <v>500000</v>
-      </c>
-      <c r="G27" s="5">
-        <v>200000</v>
-      </c>
-      <c r="H27" s="5">
-        <v>100000</v>
-      </c>
-      <c r="I27" s="5">
-        <v>800000</v>
-      </c>
-      <c r="J27" s="5">
-        <v>1990000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>23</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D28" s="5">
-        <v>100000</v>
-      </c>
-      <c r="E28" s="5">
-        <v>0</v>
-      </c>
-      <c r="F28" s="5">
-        <v>0</v>
-      </c>
-      <c r="G28" s="5">
-        <v>200000</v>
-      </c>
-      <c r="H28" s="5">
-        <v>0</v>
-      </c>
-      <c r="I28" s="5">
-        <v>200000</v>
-      </c>
-      <c r="J28" s="5">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>24</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D29" s="5">
-        <v>100000</v>
-      </c>
-      <c r="E29" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F29" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G29" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H29" s="5">
-        <v>100000</v>
-      </c>
-      <c r="I29" s="5">
-        <v>750000</v>
-      </c>
-      <c r="J29" s="5">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>25</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D30" s="5">
-        <v>300000</v>
-      </c>
-      <c r="E30" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F30" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G30" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H30" s="5">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5">
-        <v>650000</v>
-      </c>
-      <c r="J30" s="5">
-        <v>1050000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>26</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D31" s="5">
-        <v>0</v>
-      </c>
-      <c r="E31" s="5">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G31" s="5">
-        <v>0</v>
-      </c>
-      <c r="H31" s="5">
-        <v>0</v>
-      </c>
-      <c r="I31" s="5">
-        <v>250000</v>
-      </c>
-      <c r="J31" s="5">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="21">
-        <v>27</v>
-      </c>
-      <c r="B32" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="D32" s="22">
-        <v>0</v>
-      </c>
-      <c r="E32" s="22">
-        <v>0</v>
-      </c>
-      <c r="F32" s="22">
-        <v>0</v>
-      </c>
-      <c r="G32" s="22">
-        <v>0</v>
-      </c>
-      <c r="H32" s="22">
-        <v>0</v>
-      </c>
-      <c r="I32" s="22">
-        <v>0</v>
-      </c>
-      <c r="J32" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>28</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F33" s="5">
-        <v>0</v>
-      </c>
-      <c r="G33" s="5">
-        <v>0</v>
-      </c>
-      <c r="H33" s="5">
-        <v>200000</v>
-      </c>
-      <c r="I33" s="5">
-        <v>200000</v>
-      </c>
-      <c r="J33" s="5">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>29</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D34" s="5">
-        <v>0</v>
-      </c>
-      <c r="E34" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F34" s="5">
-        <v>0</v>
-      </c>
-      <c r="G34" s="5">
-        <v>0</v>
-      </c>
-      <c r="H34" s="5">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>30</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D35" s="5">
-        <v>200000</v>
-      </c>
-      <c r="E35" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F35" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G35" s="5">
-        <v>200000</v>
-      </c>
-      <c r="H35" s="5">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5">
-        <v>450000</v>
-      </c>
-      <c r="J35" s="5">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>31</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D36" s="5">
-        <v>80000</v>
-      </c>
-      <c r="E36" s="5">
-        <v>0</v>
-      </c>
-      <c r="F36" s="5">
-        <v>0</v>
-      </c>
-      <c r="G36" s="5">
-        <v>400000</v>
-      </c>
-      <c r="H36" s="5">
-        <v>100000</v>
-      </c>
-      <c r="I36" s="5">
-        <v>500000</v>
-      </c>
-      <c r="J36" s="5">
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
-        <v>32</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D37" s="5">
-        <v>500000</v>
-      </c>
-      <c r="E37" s="5">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G37" s="5">
-        <v>200000</v>
-      </c>
-      <c r="H37" s="5">
-        <v>0</v>
-      </c>
-      <c r="I37" s="5">
-        <v>450000</v>
-      </c>
-      <c r="J37" s="5">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="21">
-        <v>33</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="D38" s="22">
-        <v>0</v>
-      </c>
-      <c r="E38" s="22">
-        <v>0</v>
-      </c>
-      <c r="F38" s="22">
-        <v>0</v>
-      </c>
-      <c r="G38" s="22">
-        <v>0</v>
-      </c>
-      <c r="H38" s="22">
-        <v>0</v>
-      </c>
-      <c r="I38" s="22">
-        <v>0</v>
-      </c>
-      <c r="J38" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
-        <v>34</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D39" s="5">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5">
-        <v>0</v>
-      </c>
-      <c r="G39" s="5">
-        <v>0</v>
-      </c>
-      <c r="H39" s="5">
-        <v>100000</v>
-      </c>
-      <c r="I39" s="5">
-        <v>100000</v>
-      </c>
-      <c r="J39" s="5">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>35</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D40" s="5">
-        <v>0</v>
-      </c>
-      <c r="E40" s="5">
-        <v>0</v>
-      </c>
-      <c r="F40" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G40" s="5">
-        <v>0</v>
-      </c>
-      <c r="H40" s="5">
-        <v>0</v>
-      </c>
-      <c r="I40" s="5">
-        <v>250000</v>
-      </c>
-      <c r="J40" s="5">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
-        <v>36</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D41" s="5">
-        <v>300000</v>
-      </c>
-      <c r="E41" s="5">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5">
-        <v>0</v>
-      </c>
-      <c r="G41" s="5">
-        <v>0</v>
-      </c>
-      <c r="H41" s="5">
-        <v>100000</v>
-      </c>
-      <c r="I41" s="5">
-        <v>100000</v>
-      </c>
-      <c r="J41" s="5">
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
-        <v>37</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D42" s="5">
-        <v>400000</v>
-      </c>
-      <c r="E42" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F42" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G42" s="5">
-        <v>200000</v>
-      </c>
-      <c r="H42" s="5">
-        <v>0</v>
-      </c>
-      <c r="I42" s="5">
-        <v>450000</v>
-      </c>
-      <c r="J42" s="5">
-        <v>950000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="33" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <v>38</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="D43" s="5">
-        <v>400000</v>
-      </c>
-      <c r="E43" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F43" s="5">
-        <v>250000</v>
-      </c>
-      <c r="G43" s="5">
-        <v>200000</v>
-      </c>
-      <c r="H43" s="5">
-        <v>200000</v>
-      </c>
-      <c r="I43" s="5">
-        <v>650000</v>
-      </c>
-      <c r="J43" s="5">
-        <v>1150000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="21">
-        <v>39</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="D44" s="22">
-        <v>0</v>
-      </c>
-      <c r="E44" s="22">
-        <v>0</v>
-      </c>
-      <c r="F44" s="22">
-        <v>0</v>
-      </c>
-      <c r="G44" s="22">
-        <v>0</v>
-      </c>
-      <c r="H44" s="22">
-        <v>0</v>
-      </c>
-      <c r="I44" s="22">
-        <v>0</v>
-      </c>
-      <c r="J44" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="21">
-        <v>40</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="D45" s="22">
-        <v>0</v>
-      </c>
-      <c r="E45" s="22">
-        <v>0</v>
-      </c>
-      <c r="F45" s="22">
-        <v>0</v>
-      </c>
-      <c r="G45" s="22">
-        <v>0</v>
-      </c>
-      <c r="H45" s="22">
-        <v>0</v>
-      </c>
-      <c r="I45" s="22">
-        <v>0</v>
-      </c>
-      <c r="J45" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
-        <v>41</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D46" s="5">
-        <v>0</v>
-      </c>
-      <c r="E46" s="5">
-        <v>0</v>
-      </c>
-      <c r="F46" s="5">
-        <v>0</v>
-      </c>
-      <c r="G46" s="5">
-        <v>0</v>
-      </c>
-      <c r="H46" s="5">
-        <v>100000</v>
-      </c>
-      <c r="I46" s="5">
-        <v>100000</v>
-      </c>
-      <c r="J46" s="5">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="48" t="s">
-        <v>219</v>
-      </c>
-      <c r="B47" s="34"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="49"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="49"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
-        <v>42</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D48" s="5">
-        <v>0</v>
-      </c>
-      <c r="E48" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F48" s="5">
-        <v>0</v>
-      </c>
-      <c r="G48" s="5">
-        <v>0</v>
-      </c>
-      <c r="H48" s="5">
-        <v>0</v>
-      </c>
-      <c r="I48" s="5">
-        <v>0</v>
-      </c>
-      <c r="J48" s="5">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
-        <v>43</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D49" s="5">
-        <v>0</v>
-      </c>
-      <c r="E49" s="5">
-        <v>100000</v>
-      </c>
-      <c r="F49" s="5">
-        <v>0</v>
-      </c>
-      <c r="G49" s="5">
-        <v>0</v>
-      </c>
-      <c r="H49" s="5">
-        <v>0</v>
-      </c>
-      <c r="I49" s="5">
-        <v>0</v>
-      </c>
-      <c r="J49" s="5">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
-        <v>44</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D50" s="5">
-        <v>0</v>
-      </c>
-      <c r="E50" s="5">
-        <v>200000</v>
-      </c>
-      <c r="F50" s="5">
-        <v>0</v>
-      </c>
-      <c r="G50" s="5">
-        <v>0</v>
-      </c>
-      <c r="H50" s="5">
-        <v>0</v>
-      </c>
-      <c r="I50" s="5">
-        <v>0</v>
-      </c>
-      <c r="J50" s="5">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="B51" s="50"/>
-      <c r="C51" s="50"/>
-      <c r="D51" s="8">
-        <v>14530000</v>
-      </c>
-      <c r="E51" s="8">
-        <v>2000008</v>
-      </c>
-      <c r="F51" s="8">
-        <v>5500000</v>
-      </c>
-      <c r="G51" s="8">
-        <v>7000000</v>
-      </c>
-      <c r="H51" s="8">
-        <v>2200000</v>
-      </c>
-      <c r="I51" s="8">
-        <v>14700000</v>
-      </c>
-      <c r="J51" s="8">
-        <v>31230008</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="J4:J5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
